--- a/ru/downloads/data-excel/6.1.1.xlsx
+++ b/ru/downloads/data-excel/6.1.1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14175" windowHeight="8070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -675,13 +675,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="33.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="57" customHeight="1">
+    <row r="1" spans="1:17" ht="57" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>42</v>
       </c>
@@ -692,7 +692,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="18" customFormat="1" ht="14.25" customHeight="1">
+    <row r="2" spans="1:17" s="18" customFormat="1" ht="14.25" customHeight="1">
       <c r="A2" s="19" t="s">
         <v>43</v>
       </c>
@@ -703,7 +703,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="14.25" customHeight="1" thickBot="1">
+    <row r="3" spans="1:17" ht="14.25" customHeight="1" thickBot="1">
       <c r="A3" s="8"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -720,8 +720,9 @@
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
-    </row>
-    <row r="4" spans="1:16" s="5" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="Q3" s="8"/>
+    </row>
+    <row r="4" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="A4" s="14" t="s">
         <v>14</v>
       </c>
@@ -770,8 +771,11 @@
       <c r="P4" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" s="5" customFormat="1" ht="15" customHeight="1">
+      <c r="Q4" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -820,8 +824,11 @@
       <c r="P5" s="16">
         <v>95.373053602652249</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="16">
+        <v>96.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
@@ -870,8 +877,11 @@
       <c r="P6" s="17">
         <v>99.709525489789883</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="17">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
@@ -920,8 +930,11 @@
       <c r="P7" s="17">
         <v>92.894381967187897</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7" s="17">
+        <v>94.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -970,8 +983,11 @@
       <c r="P8" s="17">
         <v>87.728978608179318</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="17">
+        <v>90.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
@@ -1020,8 +1036,11 @@
       <c r="P9" s="17">
         <v>92.40411808116626</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="17">
+        <v>91.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1070,8 +1089,11 @@
       <c r="P10" s="17">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="17">
+        <v>97.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -1120,8 +1142,11 @@
       <c r="P11" s="17">
         <v>98.289581076331672</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="17">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -1170,8 +1195,11 @@
       <c r="P12" s="17">
         <v>89.917403585977922</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="17">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
@@ -1220,8 +1248,11 @@
       <c r="P13" s="17">
         <v>99.605426405132818</v>
       </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="17">
+        <v>99.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
         <v>23</v>
       </c>
@@ -1270,8 +1301,11 @@
       <c r="P14" s="17">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
         <v>24</v>
       </c>
@@ -1320,8 +1354,11 @@
       <c r="P15" s="17">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" ht="15.75" thickBot="1">
+      <c r="Q15" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="15.75" thickBot="1">
       <c r="A16" s="9" t="s">
         <v>25</v>
       </c>
@@ -1368,6 +1405,9 @@
         <v>100</v>
       </c>
       <c r="P16" s="13">
+        <v>100</v>
+      </c>
+      <c r="Q16" s="13">
         <v>100</v>
       </c>
     </row>
